--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>94982</v>
+        <v>94985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>94982</v>
+        <v>94985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332356</v>
+        <v>123332354</v>
       </c>
       <c r="B2" t="n">
-        <v>94985</v>
+        <v>94987</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441851</v>
+        <v>441846</v>
       </c>
       <c r="R2" t="n">
-        <v>6461425</v>
+        <v>6461420</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332354</v>
+        <v>123332356</v>
       </c>
       <c r="B3" t="n">
-        <v>94985</v>
+        <v>94987</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441846</v>
+        <v>441851</v>
       </c>
       <c r="R3" t="n">
-        <v>6461420</v>
+        <v>6461425</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332354</v>
+        <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>94987</v>
+        <v>94993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441846</v>
+        <v>441851</v>
       </c>
       <c r="R2" t="n">
-        <v>6461420</v>
+        <v>6461425</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332356</v>
+        <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>94987</v>
+        <v>94993</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441851</v>
+        <v>441846</v>
       </c>
       <c r="R3" t="n">
-        <v>6461425</v>
+        <v>6461420</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>94993</v>
+        <v>94996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>94993</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332356</v>
       </c>
       <c r="B2" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332354</v>
       </c>
       <c r="B3" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332356</v>
+        <v>123332354</v>
       </c>
       <c r="B2" t="n">
         <v>95529</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441851</v>
+        <v>441846</v>
       </c>
       <c r="R2" t="n">
-        <v>6461425</v>
+        <v>6461420</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332354</v>
+        <v>123332356</v>
       </c>
       <c r="B3" t="n">
         <v>95529</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441846</v>
+        <v>441851</v>
       </c>
       <c r="R3" t="n">
-        <v>6461420</v>
+        <v>6461425</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 8866-2025 artfynd.xlsx
+++ b/artfynd/A 8866-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332354</v>
+        <v>123332356</v>
       </c>
       <c r="B2" t="n">
         <v>95529</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441846</v>
+        <v>441851</v>
       </c>
       <c r="R2" t="n">
-        <v>6461420</v>
+        <v>6461425</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332356</v>
+        <v>123332354</v>
       </c>
       <c r="B3" t="n">
         <v>95529</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441851</v>
+        <v>441846</v>
       </c>
       <c r="R3" t="n">
-        <v>6461425</v>
+        <v>6461420</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
